--- a/tracking/compare/tracking-list.xlsx
+++ b/tracking/compare/tracking-list.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCFE36B-87DB-4271-871B-C073992232F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4CBC40-F957-4364-896F-8711AC843B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D2D124BC-3906-40C8-BA6E-71B75F658845}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D2D124BC-3906-40C8-BA6E-71B75F658845}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="300">
   <si>
     <t>ID</t>
   </si>
@@ -864,13 +853,85 @@
   </si>
   <si>
     <t>한신휴플러스타운3차</t>
+  </si>
+  <si>
+    <t>광장힐스테이트</t>
+  </si>
+  <si>
+    <t>광장현대5단지</t>
+  </si>
+  <si>
+    <t>현대8단지</t>
+  </si>
+  <si>
+    <t>현대프라임</t>
+  </si>
+  <si>
+    <t>구의현대2단지</t>
+  </si>
+  <si>
+    <t>e편한세상광진그랜드파크</t>
+  </si>
+  <si>
+    <t>롯데캐슬이스트폴</t>
+  </si>
+  <si>
+    <t>롯데캐슬리버파크시그니처</t>
+  </si>
+  <si>
+    <t>우성1차</t>
+  </si>
+  <si>
+    <t>자양우성3차</t>
+  </si>
+  <si>
+    <t>자양하늘채베르</t>
+  </si>
+  <si>
+    <t>래미안파크스위트</t>
+  </si>
+  <si>
+    <t>영동한양1차</t>
+  </si>
+  <si>
+    <t>청담르엘</t>
+  </si>
+  <si>
+    <t>래미안라클래시</t>
+  </si>
+  <si>
+    <t>래미안대치팰리스</t>
+  </si>
+  <si>
+    <t>도곡렉슬</t>
+  </si>
+  <si>
+    <t>대치르엘</t>
+  </si>
+  <si>
+    <t>개포자이프레지던스</t>
+  </si>
+  <si>
+    <t>디에이치퍼스티어아이파크</t>
+  </si>
+  <si>
+    <t>디에이치자이개포</t>
+  </si>
+  <si>
+    <t>삼익</t>
+  </si>
+  <si>
+    <t>강남자곡아이파크</t>
+  </si>
+  <si>
+    <t>세곡푸르지오</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -989,7 +1050,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1029,6 +1090,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1047,9 +1111,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1087,7 +1151,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1193,7 +1257,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1335,7 +1399,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1343,13 +1407,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A24302-B46C-46ED-B213-366C3ADB75BA}">
-  <dimension ref="A1:C276"/>
-  <sheetFormatPr defaultRowHeight="10.8"/>
+  <dimension ref="A1:C300"/>
+  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="39.75" customWidth="1"/>
+    <col min="2" max="2" width="39.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.8" thickBot="1">
+    <row r="1" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1360,7 +1424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.8" thickBot="1">
+    <row r="2" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>113292</v>
       </c>
@@ -1371,7 +1435,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="13.8" thickBot="1">
+    <row r="3" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>131685</v>
       </c>
@@ -1382,7 +1446,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="13.8" thickBot="1">
+    <row r="4" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>100304</v>
       </c>
@@ -1393,7 +1457,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.8" thickBot="1">
+    <row r="5" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>109124</v>
       </c>
@@ -1404,7 +1468,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="13.8" thickBot="1">
+    <row r="6" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>113097</v>
       </c>
@@ -1415,7 +1479,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="13.8" thickBot="1">
+    <row r="7" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>22491</v>
       </c>
@@ -1426,7 +1490,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="13.8" thickBot="1">
+    <row r="8" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>3381</v>
       </c>
@@ -1437,7 +1501,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.8" thickBot="1">
+    <row r="9" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>364</v>
       </c>
@@ -1448,7 +1512,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.8" thickBot="1">
+    <row r="10" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>3280</v>
       </c>
@@ -1459,7 +1523,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.8" thickBot="1">
+    <row r="11" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>102142</v>
       </c>
@@ -1470,7 +1534,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="13.8" thickBot="1">
+    <row r="12" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>111467</v>
       </c>
@@ -1481,7 +1545,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.8" thickBot="1">
+    <row r="13" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>115936</v>
       </c>
@@ -1492,7 +1556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="13.8" thickBot="1">
+    <row r="14" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>391</v>
       </c>
@@ -1503,7 +1567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.8" thickBot="1">
+    <row r="15" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>123898</v>
       </c>
@@ -1514,7 +1578,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="13.8" thickBot="1">
+    <row r="16" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>27508</v>
       </c>
@@ -1525,7 +1589,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="13.8" thickBot="1">
+    <row r="17" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>27570</v>
       </c>
@@ -1536,7 +1600,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="13.8" thickBot="1">
+    <row r="18" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>27371</v>
       </c>
@@ -1547,7 +1611,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="13.8" thickBot="1">
+    <row r="19" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>3621</v>
       </c>
@@ -1558,7 +1622,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="13.8" thickBot="1">
+    <row r="20" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>2623</v>
       </c>
@@ -1569,7 +1633,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="13.8" thickBot="1">
+    <row r="21" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>2797</v>
       </c>
@@ -1580,7 +1644,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="13.8" thickBot="1">
+    <row r="22" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>1980</v>
       </c>
@@ -1591,7 +1655,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="13.8" thickBot="1">
+    <row r="23" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>1923</v>
       </c>
@@ -1602,7 +1666,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="13.8" thickBot="1">
+    <row r="24" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>1687</v>
       </c>
@@ -1613,7 +1677,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="13.8" thickBot="1">
+    <row r="25" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>8297</v>
       </c>
@@ -1624,7 +1688,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="13.8" thickBot="1">
+    <row r="26" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>2591</v>
       </c>
@@ -1635,7 +1699,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="13.8" thickBot="1">
+    <row r="27" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>2789</v>
       </c>
@@ -1646,7 +1710,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="13.8" thickBot="1">
+    <row r="28" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>1525</v>
       </c>
@@ -1657,7 +1721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="13.8" thickBot="1">
+    <row r="29" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>2537</v>
       </c>
@@ -1668,7 +1732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="13.8" thickBot="1">
+    <row r="30" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>2198</v>
       </c>
@@ -1679,7 +1743,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="13.8" thickBot="1">
+    <row r="31" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>3457</v>
       </c>
@@ -1690,7 +1754,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="13.8" thickBot="1">
+    <row r="32" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>2981</v>
       </c>
@@ -1701,7 +1765,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="13.8" thickBot="1">
+    <row r="33" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>121987</v>
       </c>
@@ -1712,7 +1776,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="13.8" thickBot="1">
+    <row r="34" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>3452</v>
       </c>
@@ -1723,7 +1787,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="13.8" thickBot="1">
+    <row r="35" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>3450</v>
       </c>
@@ -1734,7 +1798,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="13.8" thickBot="1">
+    <row r="36" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>1216</v>
       </c>
@@ -1745,7 +1809,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="13.8" thickBot="1">
+    <row r="37" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>120522</v>
       </c>
@@ -1756,7 +1820,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="13.8" thickBot="1">
+    <row r="38" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>117254</v>
       </c>
@@ -1767,7 +1831,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="13.8" thickBot="1">
+    <row r="39" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>128302</v>
       </c>
@@ -1778,7 +1842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="13.8" thickBot="1">
+    <row r="40" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>111396</v>
       </c>
@@ -1789,7 +1853,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="13.8" thickBot="1">
+    <row r="41" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>103797</v>
       </c>
@@ -1800,7 +1864,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="13.8" thickBot="1">
+    <row r="42" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>113059</v>
       </c>
@@ -1811,7 +1875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="13.8" thickBot="1">
+    <row r="43" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>125111</v>
       </c>
@@ -1822,7 +1886,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="13.8" thickBot="1">
+    <row r="44" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>133184</v>
       </c>
@@ -1833,7 +1897,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="13.8" thickBot="1">
+    <row r="45" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>26192</v>
       </c>
@@ -1844,7 +1908,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="13.8" thickBot="1">
+    <row r="46" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>3376</v>
       </c>
@@ -1855,7 +1919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="13.8" thickBot="1">
+    <row r="47" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>22636</v>
       </c>
@@ -1866,7 +1930,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="13.8" thickBot="1">
+    <row r="48" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>119787</v>
       </c>
@@ -1877,7 +1941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="13.8" thickBot="1">
+    <row r="49" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>112482</v>
       </c>
@@ -1888,7 +1952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="13.8" thickBot="1">
+    <row r="50" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>8199</v>
       </c>
@@ -1899,7 +1963,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="13.8" thickBot="1">
+    <row r="51" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>8791</v>
       </c>
@@ -1910,7 +1974,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="13.8" thickBot="1">
+    <row r="52" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>111555</v>
       </c>
@@ -1921,7 +1985,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="13.8" thickBot="1">
+    <row r="53" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>120540</v>
       </c>
@@ -1932,7 +1996,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="13.8" thickBot="1">
+    <row r="54" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>3093</v>
       </c>
@@ -1943,7 +2007,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="13.8" thickBot="1">
+    <row r="55" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>102536</v>
       </c>
@@ -1954,7 +2018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="13.8" thickBot="1">
+    <row r="56" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>8484</v>
       </c>
@@ -1965,7 +2029,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="13.8" thickBot="1">
+    <row r="57" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>109948</v>
       </c>
@@ -1976,7 +2040,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="13.8" thickBot="1">
+    <row r="58" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>115593</v>
       </c>
@@ -1987,7 +2051,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="13.8" thickBot="1">
+    <row r="59" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>9390</v>
       </c>
@@ -1998,7 +2062,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="13.8" thickBot="1">
+    <row r="60" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>126607</v>
       </c>
@@ -2009,7 +2073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="13.8" thickBot="1">
+    <row r="61" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>8292</v>
       </c>
@@ -2020,7 +2084,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="13.8" thickBot="1">
+    <row r="62" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>2535</v>
       </c>
@@ -2031,7 +2095,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="13.8" thickBot="1">
+    <row r="63" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>24301</v>
       </c>
@@ -2042,7 +2106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="13.8" thickBot="1">
+    <row r="64" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>119652</v>
       </c>
@@ -2053,7 +2117,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="13.8" thickBot="1">
+    <row r="65" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>105414</v>
       </c>
@@ -2064,7 +2128,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="13.8" thickBot="1">
+    <row r="66" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>107542</v>
       </c>
@@ -2075,7 +2139,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="13.8" thickBot="1">
+    <row r="67" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>19204</v>
       </c>
@@ -2086,7 +2150,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="13.8" thickBot="1">
+    <row r="68" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>19672</v>
       </c>
@@ -2097,7 +2161,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="13.8" thickBot="1">
+    <row r="69" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>26216</v>
       </c>
@@ -2108,7 +2172,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="13.8" thickBot="1">
+    <row r="70" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>113538</v>
       </c>
@@ -2119,7 +2183,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="13.8" thickBot="1">
+    <row r="71" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>114379</v>
       </c>
@@ -2130,7 +2194,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="13.8" thickBot="1">
+    <row r="72" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>114415</v>
       </c>
@@ -2141,7 +2205,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="13.8" thickBot="1">
+    <row r="73" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>115473</v>
       </c>
@@ -2152,7 +2216,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="13.8" thickBot="1">
+    <row r="74" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>119469</v>
       </c>
@@ -2163,7 +2227,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="13.8" thickBot="1">
+    <row r="75" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>111626</v>
       </c>
@@ -2174,7 +2238,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="13.8" thickBot="1">
+    <row r="76" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>22746</v>
       </c>
@@ -2185,7 +2249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="13.8" thickBot="1">
+    <row r="77" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>22675</v>
       </c>
@@ -2196,7 +2260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="13.8" thickBot="1">
+    <row r="78" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>15011</v>
       </c>
@@ -2207,7 +2271,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="13.8" thickBot="1">
+    <row r="79" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>111515</v>
       </c>
@@ -2218,7 +2282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="13.8" thickBot="1">
+    <row r="80" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>103139</v>
       </c>
@@ -2229,7 +2293,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="13.8" thickBot="1">
+    <row r="81" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>610</v>
       </c>
@@ -2240,7 +2304,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="13.8" thickBot="1">
+    <row r="82" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>107544</v>
       </c>
@@ -2251,7 +2315,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="13.8" thickBot="1">
+    <row r="83" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>104126</v>
       </c>
@@ -2262,7 +2326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="13.8" thickBot="1">
+    <row r="84" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>26107</v>
       </c>
@@ -2273,7 +2337,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="13.8" thickBot="1">
+    <row r="85" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>115046</v>
       </c>
@@ -2284,7 +2348,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="13.8" thickBot="1">
+    <row r="86" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>127132</v>
       </c>
@@ -2295,7 +2359,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="13.8" thickBot="1">
+    <row r="87" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>102313</v>
       </c>
@@ -2306,7 +2370,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="13.8" thickBot="1">
+    <row r="88" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>114809</v>
       </c>
@@ -2317,7 +2381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="13.8" thickBot="1">
+    <row r="89" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>2988</v>
       </c>
@@ -2328,7 +2392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="13.8" thickBot="1">
+    <row r="90" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>3034</v>
       </c>
@@ -2339,7 +2403,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="13.8" thickBot="1">
+    <row r="91" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>148337</v>
       </c>
@@ -2350,7 +2414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="13.8" thickBot="1">
+    <row r="92" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>8877</v>
       </c>
@@ -2361,7 +2425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="13.8" thickBot="1">
+    <row r="93" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>3333</v>
       </c>
@@ -2372,7 +2436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="13.8" thickBot="1">
+    <row r="94" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>19220</v>
       </c>
@@ -2383,7 +2447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="13.8" thickBot="1">
+    <row r="95" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>8895</v>
       </c>
@@ -2394,7 +2458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="13.8" thickBot="1">
+    <row r="96" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>18210</v>
       </c>
@@ -2405,7 +2469,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="13.8" thickBot="1">
+    <row r="97" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>109379</v>
       </c>
@@ -2416,7 +2480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="13.8" thickBot="1">
+    <row r="98" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>22124</v>
       </c>
@@ -2427,7 +2491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="13.8" thickBot="1">
+    <row r="99" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>22788</v>
       </c>
@@ -2438,7 +2502,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="13.8" thickBot="1">
+    <row r="100" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>109250</v>
       </c>
@@ -2449,7 +2513,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="13.8" thickBot="1">
+    <row r="101" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>3832</v>
       </c>
@@ -2460,7 +2524,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="13.8" thickBot="1">
+    <row r="102" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>107404</v>
       </c>
@@ -2471,7 +2535,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="13.8" thickBot="1">
+    <row r="103" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>100310</v>
       </c>
@@ -2482,7 +2546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="13.8" thickBot="1">
+    <row r="104" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>27820</v>
       </c>
@@ -2493,7 +2557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="13.8" thickBot="1">
+    <row r="105" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>24845</v>
       </c>
@@ -2504,7 +2568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="13.8" thickBot="1">
+    <row r="106" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>24911</v>
       </c>
@@ -2515,7 +2579,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="13.8" thickBot="1">
+    <row r="107" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>3833</v>
       </c>
@@ -2526,7 +2590,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="13.8" thickBot="1">
+    <row r="108" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>1238</v>
       </c>
@@ -2537,7 +2601,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="13.8" thickBot="1">
+    <row r="109" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>111330</v>
       </c>
@@ -2548,7 +2612,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="13.8" thickBot="1">
+    <row r="110" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>126062</v>
       </c>
@@ -2559,7 +2623,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="13.8" thickBot="1">
+    <row r="111" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>26160</v>
       </c>
@@ -2570,7 +2634,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="13.8" thickBot="1">
+    <row r="112" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>26834</v>
       </c>
@@ -2581,7 +2645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="13.8" thickBot="1">
+    <row r="113" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>25827</v>
       </c>
@@ -2592,7 +2656,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="13.8" thickBot="1">
+    <row r="114" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>1191</v>
       </c>
@@ -2603,7 +2667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="13.8" thickBot="1">
+    <row r="115" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>9348</v>
       </c>
@@ -2614,7 +2678,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="13.8" thickBot="1">
+    <row r="116" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>109051</v>
       </c>
@@ -2625,7 +2689,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="13.8" thickBot="1">
+    <row r="117" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>127574</v>
       </c>
@@ -2636,7 +2700,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="13.8" thickBot="1">
+    <row r="118" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>122863</v>
       </c>
@@ -2647,7 +2711,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="13.8" thickBot="1">
+    <row r="119" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>2990</v>
       </c>
@@ -2658,7 +2722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="13.8" thickBot="1">
+    <row r="120" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>114972</v>
       </c>
@@ -2669,7 +2733,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="13.8" thickBot="1">
+    <row r="121" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>659</v>
       </c>
@@ -2680,7 +2744,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="13.8" thickBot="1">
+    <row r="122" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>1204</v>
       </c>
@@ -2691,7 +2755,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="13.8" thickBot="1">
+    <row r="123" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>3774</v>
       </c>
@@ -2702,7 +2766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="13.8" thickBot="1">
+    <row r="124" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>121979</v>
       </c>
@@ -2713,7 +2777,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="13.8" thickBot="1">
+    <row r="125" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>130826</v>
       </c>
@@ -2724,7 +2788,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="13.8" thickBot="1">
+    <row r="126" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>17469</v>
       </c>
@@ -2735,7 +2799,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="13.8" thickBot="1">
+    <row r="127" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>113008</v>
       </c>
@@ -2746,7 +2810,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="13.8" thickBot="1">
+    <row r="128" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>10307</v>
       </c>
@@ -2757,7 +2821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="13.8" thickBot="1">
+    <row r="129" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>24406</v>
       </c>
@@ -2768,7 +2832,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="13.8" thickBot="1">
+    <row r="130" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>117329</v>
       </c>
@@ -2779,7 +2843,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="13.8" thickBot="1">
+    <row r="131" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>107728</v>
       </c>
@@ -2790,7 +2854,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="13.8" thickBot="1">
+    <row r="132" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>135411</v>
       </c>
@@ -2801,7 +2865,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="13.8" thickBot="1">
+    <row r="133" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>109266</v>
       </c>
@@ -2812,7 +2876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="13.8" thickBot="1">
+    <row r="134" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>110632</v>
       </c>
@@ -2823,7 +2887,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="13.8" thickBot="1">
+    <row r="135" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>107715</v>
       </c>
@@ -2834,7 +2898,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="13.8" thickBot="1">
+    <row r="136" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>118771</v>
       </c>
@@ -2845,7 +2909,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="13.8" thickBot="1">
+    <row r="137" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>102283</v>
       </c>
@@ -2856,7 +2920,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="13.8" thickBot="1">
+    <row r="138" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>1736</v>
       </c>
@@ -2867,7 +2931,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="13.8" thickBot="1">
+    <row r="139" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>126153</v>
       </c>
@@ -2878,7 +2942,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="13.8" thickBot="1">
+    <row r="140" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>118718</v>
       </c>
@@ -2889,7 +2953,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="13.8" thickBot="1">
+    <row r="141" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>18542</v>
       </c>
@@ -2900,7 +2964,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="13.8" thickBot="1">
+    <row r="142" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>27291</v>
       </c>
@@ -2911,7 +2975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="13.8" thickBot="1">
+    <row r="143" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>1735</v>
       </c>
@@ -2922,7 +2986,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="13.8" thickBot="1">
+    <row r="144" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>26187</v>
       </c>
@@ -2933,7 +2997,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="13.8" thickBot="1">
+    <row r="145" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>110209</v>
       </c>
@@ -2944,7 +3008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="13.8" thickBot="1">
+    <row r="146" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>110092</v>
       </c>
@@ -2955,7 +3019,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="13.8" thickBot="1">
+    <row r="147" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>849</v>
       </c>
@@ -2966,7 +3030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="13.8" thickBot="1">
+    <row r="148" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>26046</v>
       </c>
@@ -2977,7 +3041,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="13.8" thickBot="1">
+    <row r="149" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>11567</v>
       </c>
@@ -2988,7 +3052,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="13.8" thickBot="1">
+    <row r="150" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>941</v>
       </c>
@@ -2999,7 +3063,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="13.8" thickBot="1">
+    <row r="151" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>108064</v>
       </c>
@@ -3010,7 +3074,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="13.8" thickBot="1">
+    <row r="152" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>124802</v>
       </c>
@@ -3021,7 +3085,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="13.8" thickBot="1">
+    <row r="153" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>945</v>
       </c>
@@ -3032,7 +3096,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="13.8" thickBot="1">
+    <row r="154" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>128515</v>
       </c>
@@ -3043,7 +3107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="13.8" thickBot="1">
+    <row r="155" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>114768</v>
       </c>
@@ -3054,7 +3118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="13.8" thickBot="1">
+    <row r="156" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>128027</v>
       </c>
@@ -3065,7 +3129,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="13.8" thickBot="1">
+    <row r="157" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>27424</v>
       </c>
@@ -3076,7 +3140,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="13.8" thickBot="1">
+    <row r="158" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>8104</v>
       </c>
@@ -3087,7 +3151,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="13.8" thickBot="1">
+    <row r="159" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>556</v>
       </c>
@@ -3098,7 +3162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="13.8" thickBot="1">
+    <row r="160" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>110938</v>
       </c>
@@ -3109,7 +3173,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="13.8" thickBot="1">
+    <row r="161" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>103136</v>
       </c>
@@ -3120,7 +3184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="13.8" thickBot="1">
+    <row r="162" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>1179</v>
       </c>
@@ -3131,7 +3195,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="13.8" thickBot="1">
+    <row r="163" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>110936</v>
       </c>
@@ -3142,7 +3206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="13.8" thickBot="1">
+    <row r="164" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>109910</v>
       </c>
@@ -3153,7 +3217,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="13.8" thickBot="1">
+    <row r="165" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>2976</v>
       </c>
@@ -3164,7 +3228,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="13.8" thickBot="1">
+    <row r="166" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>10316</v>
       </c>
@@ -3175,7 +3239,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="13.8" thickBot="1">
+    <row r="167" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>111002</v>
       </c>
@@ -3186,7 +3250,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="13.8" thickBot="1">
+    <row r="168" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>9124</v>
       </c>
@@ -3197,7 +3261,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="13.8" thickBot="1">
+    <row r="169" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>119275</v>
       </c>
@@ -3208,7 +3272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="13.8" thickBot="1">
+    <row r="170" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>111575</v>
       </c>
@@ -3219,7 +3283,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="13.8" thickBot="1">
+    <row r="171" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>119053</v>
       </c>
@@ -3230,7 +3294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="13.8" thickBot="1">
+    <row r="172" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>134321</v>
       </c>
@@ -3241,7 +3305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="13.8" thickBot="1">
+    <row r="173" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>124651</v>
       </c>
@@ -3252,7 +3316,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="13.8" thickBot="1">
+    <row r="174" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>136043</v>
       </c>
@@ -3263,7 +3327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="13.8" thickBot="1">
+    <row r="175" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>26896</v>
       </c>
@@ -3274,7 +3338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="13.8" thickBot="1">
+    <row r="176" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>103025</v>
       </c>
@@ -3285,7 +3349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="13.8" thickBot="1">
+    <row r="177" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>26869</v>
       </c>
@@ -3296,7 +3360,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="13.8" thickBot="1">
+    <row r="178" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>156291</v>
       </c>
@@ -3307,7 +3371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="13.8" thickBot="1">
+    <row r="179" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>112914</v>
       </c>
@@ -3318,7 +3382,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="13.8" thickBot="1">
+    <row r="180" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>9354</v>
       </c>
@@ -3329,7 +3393,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="13.8" thickBot="1">
+    <row r="181" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>119588</v>
       </c>
@@ -3340,7 +3404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="13.8" thickBot="1">
+    <row r="182" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>119155</v>
       </c>
@@ -3351,7 +3415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="13.8" thickBot="1">
+    <row r="183" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>107072</v>
       </c>
@@ -3362,7 +3426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="13.8" thickBot="1">
+    <row r="184" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>153402</v>
       </c>
@@ -3373,7 +3437,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="13.8" thickBot="1">
+    <row r="185" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>110153</v>
       </c>
@@ -3384,7 +3448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="13.8" thickBot="1">
+    <row r="186" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>3467</v>
       </c>
@@ -3395,7 +3459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="13.8" thickBot="1">
+    <row r="187" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>100653</v>
       </c>
@@ -3406,7 +3470,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="13.8" thickBot="1">
+    <row r="188" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>3470</v>
       </c>
@@ -3417,7 +3481,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="13.8" thickBot="1">
+    <row r="189" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>815</v>
       </c>
@@ -3428,7 +3492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="13.8" thickBot="1">
+    <row r="190" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>127599</v>
       </c>
@@ -3439,7 +3503,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="13.8" thickBot="1">
+    <row r="191" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>107073</v>
       </c>
@@ -3450,7 +3514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="13.8" thickBot="1">
+    <row r="192" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>102941</v>
       </c>
@@ -3461,7 +3525,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="13.8" thickBot="1">
+    <row r="193" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>8626</v>
       </c>
@@ -3472,7 +3536,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="13.8" thickBot="1">
+    <row r="194" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>1483</v>
       </c>
@@ -3483,7 +3547,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="13.8" thickBot="1">
+    <row r="195" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>1471</v>
       </c>
@@ -3494,7 +3558,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="13.8" thickBot="1">
+    <row r="196" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
         <v>107579</v>
       </c>
@@ -3505,7 +3569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="13.8" thickBot="1">
+    <row r="197" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>2505</v>
       </c>
@@ -3516,7 +3580,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="13.8" thickBot="1">
+    <row r="198" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>1467</v>
       </c>
@@ -3527,7 +3591,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="13.8" thickBot="1">
+    <row r="199" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>154917</v>
       </c>
@@ -3538,7 +3602,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="13.8" thickBot="1">
+    <row r="200" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>142558</v>
       </c>
@@ -3549,7 +3613,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="13.8" thickBot="1">
+    <row r="201" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>3081</v>
       </c>
@@ -3560,7 +3624,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="13.8" thickBot="1">
+    <row r="202" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>126060</v>
       </c>
@@ -3571,7 +3635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="13.8" thickBot="1">
+    <row r="203" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>102312</v>
       </c>
@@ -3582,7 +3646,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="13.8" thickBot="1">
+    <row r="204" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>144023</v>
       </c>
@@ -3593,7 +3657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="13.8" thickBot="1">
+    <row r="205" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="7">
         <v>101273</v>
       </c>
@@ -3604,7 +3668,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="13.8" thickBot="1">
+    <row r="206" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="8">
         <v>111038</v>
       </c>
@@ -3615,7 +3679,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="13.8" thickBot="1">
+    <row r="207" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="7">
         <v>102119</v>
       </c>
@@ -3626,7 +3690,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="13.8" thickBot="1">
+    <row r="208" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="8">
         <v>109412</v>
       </c>
@@ -3637,7 +3701,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="13.8" thickBot="1">
+    <row r="209" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="7">
         <v>103518</v>
       </c>
@@ -3648,7 +3712,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="13.8" thickBot="1">
+    <row r="210" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
         <v>105153</v>
       </c>
@@ -3659,7 +3723,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="13.8" thickBot="1">
+    <row r="211" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="7">
         <v>109929</v>
       </c>
@@ -3670,7 +3734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="13.8" thickBot="1">
+    <row r="212" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
         <v>1804</v>
       </c>
@@ -3681,7 +3745,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="13.8" thickBot="1">
+    <row r="213" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="7">
         <v>2490</v>
       </c>
@@ -3692,7 +3756,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="13.8" thickBot="1">
+    <row r="214" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
         <v>22911</v>
       </c>
@@ -3703,7 +3767,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="13.8" thickBot="1">
+    <row r="215" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="7">
         <v>135404</v>
       </c>
@@ -3714,7 +3778,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="13.8" thickBot="1">
+    <row r="216" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>13698</v>
       </c>
@@ -3725,7 +3789,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="13.8" thickBot="1">
+    <row r="217" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>3356</v>
       </c>
@@ -3736,7 +3800,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="13.8" thickBot="1">
+    <row r="218" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>3209</v>
       </c>
@@ -3747,7 +3811,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="13.8" thickBot="1">
+    <row r="219" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>3354</v>
       </c>
@@ -3758,7 +3822,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="13.8" thickBot="1">
+    <row r="220" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>25853</v>
       </c>
@@ -3769,7 +3833,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="13.8" thickBot="1">
+    <row r="221" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>17538</v>
       </c>
@@ -3780,7 +3844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="13.8" thickBot="1">
+    <row r="222" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>104934</v>
       </c>
@@ -3791,7 +3855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="13.8" thickBot="1">
+    <row r="223" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>3204</v>
       </c>
@@ -3802,7 +3866,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="13.8" thickBot="1">
+    <row r="224" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>8073</v>
       </c>
@@ -3813,7 +3877,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="13.8" thickBot="1">
+    <row r="225" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>103269</v>
       </c>
@@ -3824,7 +3888,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="13.8" thickBot="1">
+    <row r="226" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>119166</v>
       </c>
@@ -3835,7 +3899,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="13.8" thickBot="1">
+    <row r="227" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>103269</v>
       </c>
@@ -3846,7 +3910,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="13.8" thickBot="1">
+    <row r="228" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
         <v>26639</v>
       </c>
@@ -3857,7 +3921,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="13.8" thickBot="1">
+    <row r="229" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>3615</v>
       </c>
@@ -3868,7 +3932,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="13.8" thickBot="1">
+    <row r="230" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
         <v>8247</v>
       </c>
@@ -3879,7 +3943,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="13.8" thickBot="1">
+    <row r="231" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>1420</v>
       </c>
@@ -3890,7 +3954,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="13.8" thickBot="1">
+    <row r="232" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
         <v>103865</v>
       </c>
@@ -3901,7 +3965,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="13.8" thickBot="1">
+    <row r="233" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>14462</v>
       </c>
@@ -3912,7 +3976,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="13.8" thickBot="1">
+    <row r="234" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
         <v>110681</v>
       </c>
@@ -3923,7 +3987,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="13.8" thickBot="1">
+    <row r="235" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>102622</v>
       </c>
@@ -3934,7 +3998,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="13.8" thickBot="1">
+    <row r="236" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
         <v>127082</v>
       </c>
@@ -3945,7 +4009,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="13.8" thickBot="1">
+    <row r="237" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="7">
         <v>27540</v>
       </c>
@@ -3956,7 +4020,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="13.8" thickBot="1">
+    <row r="238" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="8">
         <v>120265</v>
       </c>
@@ -3967,7 +4031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="13.8" thickBot="1">
+    <row r="239" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="7">
         <v>108756</v>
       </c>
@@ -3978,7 +4042,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="13.8" thickBot="1">
+    <row r="240" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="7">
         <v>102634</v>
       </c>
@@ -3989,7 +4053,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="13.8" thickBot="1">
+    <row r="241" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="7">
         <v>101283</v>
       </c>
@@ -4000,7 +4064,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="13.8" thickBot="1">
+    <row r="242" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="7">
         <v>2895</v>
       </c>
@@ -4011,7 +4075,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="13.8" thickBot="1">
+    <row r="243" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>3864</v>
       </c>
@@ -4022,7 +4086,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="13.8" thickBot="1">
+    <row r="244" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="7">
         <v>121277</v>
       </c>
@@ -4033,7 +4097,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="13.8" thickBot="1">
+    <row r="245" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>3580</v>
       </c>
@@ -4044,7 +4108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="13.8" thickBot="1">
+    <row r="246" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>8386</v>
       </c>
@@ -4055,7 +4119,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="13.8" thickBot="1">
+    <row r="247" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="7">
         <v>26398</v>
       </c>
@@ -4066,7 +4130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="13.8" thickBot="1">
+    <row r="248" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>2886</v>
       </c>
@@ -4077,7 +4141,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="13.8" thickBot="1">
+    <row r="249" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="7">
         <v>7963</v>
       </c>
@@ -4088,7 +4152,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="13.8" thickBot="1">
+    <row r="250" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="7">
         <v>101480</v>
       </c>
@@ -4099,7 +4163,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="13.8" thickBot="1">
+    <row r="251" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="8">
         <v>104999</v>
       </c>
@@ -4110,7 +4174,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="13.8" thickBot="1">
+    <row r="252" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="8">
         <v>8333</v>
       </c>
@@ -4121,7 +4185,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="13.8" thickBot="1">
+    <row r="253" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="8">
         <v>127424</v>
       </c>
@@ -4132,7 +4196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="13.8" thickBot="1">
+    <row r="254" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="7">
         <v>133083</v>
       </c>
@@ -4143,7 +4207,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="13.8" thickBot="1">
+    <row r="255" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="8">
         <v>107929</v>
       </c>
@@ -4154,7 +4218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="13.8" thickBot="1">
+    <row r="256" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="8">
         <v>25902</v>
       </c>
@@ -4165,7 +4229,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="13.8" thickBot="1">
+    <row r="257" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="8">
         <v>27821</v>
       </c>
@@ -4176,7 +4240,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="13.8" thickBot="1">
+    <row r="258" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="8">
         <v>111972</v>
       </c>
@@ -4187,7 +4251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="13.8" thickBot="1">
+    <row r="259" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
         <v>159</v>
       </c>
@@ -4198,7 +4262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="13.8" thickBot="1">
+    <row r="260" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="8">
         <v>1627</v>
       </c>
@@ -4209,7 +4273,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="13.8" thickBot="1">
+    <row r="261" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="7">
         <v>1635</v>
       </c>
@@ -4220,7 +4284,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="13.8" thickBot="1">
+    <row r="262" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="8">
         <v>104347</v>
       </c>
@@ -4231,7 +4295,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="13.8" thickBot="1">
+    <row r="263" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="7">
         <v>100253</v>
       </c>
@@ -4242,7 +4306,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="13.8" thickBot="1">
+    <row r="264" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="8">
         <v>3359</v>
       </c>
@@ -4253,7 +4317,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="13.8" thickBot="1">
+    <row r="265" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="7">
         <v>147880</v>
       </c>
@@ -4264,7 +4328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="13.8" thickBot="1">
+    <row r="266" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="7">
         <v>112054</v>
       </c>
@@ -4275,7 +4339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="13.8" thickBot="1">
+    <row r="267" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="7">
         <v>8483</v>
       </c>
@@ -4286,7 +4350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="13.8" thickBot="1">
+    <row r="268" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="7">
         <v>2004</v>
       </c>
@@ -4297,7 +4361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="13.8" thickBot="1">
+    <row r="269" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="7">
         <v>19038</v>
       </c>
@@ -4308,7 +4372,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="13.8" thickBot="1">
+    <row r="270" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="7">
         <v>109366</v>
       </c>
@@ -4319,7 +4383,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="13.8" thickBot="1">
+    <row r="271" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="7">
         <v>3090</v>
       </c>
@@ -4330,7 +4394,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="13.8" thickBot="1">
+    <row r="272" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="7">
         <v>147085</v>
       </c>
@@ -4341,7 +4405,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="13.8" thickBot="1">
+    <row r="273" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="7">
         <v>121645</v>
       </c>
@@ -4352,7 +4416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="13.8" thickBot="1">
+    <row r="274" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="7">
         <v>174657</v>
       </c>
@@ -4363,7 +4427,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="13.8" thickBot="1">
+    <row r="275" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="7">
         <v>25775</v>
       </c>
@@ -4374,7 +4438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="13.8" thickBot="1">
+    <row r="276" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="7">
         <v>101284</v>
       </c>
@@ -4383,6 +4447,270 @@
       </c>
       <c r="C276" s="11">
         <v>59</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="7">
+        <v>100514</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C277" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="3">
+        <v>75</v>
+      </c>
+      <c r="B278" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C278" s="11">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="3">
+        <v>76</v>
+      </c>
+      <c r="B279" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="C279" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="3">
+        <v>84</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C280" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="3">
+        <v>81</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C281" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="3">
+        <v>125105</v>
+      </c>
+      <c r="B282" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C282" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="3">
+        <v>160239</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C283" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="3">
+        <v>135887</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C284" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="3">
+        <v>90</v>
+      </c>
+      <c r="B285" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C285" s="11">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="3">
+        <v>93</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C286" s="11">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="3">
+        <v>140746</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C287" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="3">
+        <v>112339</v>
+      </c>
+      <c r="B288" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="C288" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="4">
+        <v>494</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C289" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="4">
+        <v>182057</v>
+      </c>
+      <c r="B290" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C290" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="4">
+        <v>127477</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C291" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="3">
+        <v>180280</v>
+      </c>
+      <c r="B292" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="C292" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="3">
+        <v>11698</v>
+      </c>
+      <c r="B293" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C293" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="4">
+        <v>127973</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C294" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="3">
+        <v>128527</v>
+      </c>
+      <c r="B295" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="C295" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="3">
+        <v>134062</v>
+      </c>
+      <c r="B296" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="C296" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="3">
+        <v>121971</v>
+      </c>
+      <c r="B297" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C297" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="3">
+        <v>668</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C298" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="4">
+        <v>113680</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="C299" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="4">
+        <v>103578</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="C300" s="11">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
